--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-01).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-01).xlsx
@@ -935,94 +935,94 @@
     <t>214</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>R$ 4.752,10</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>32.8</t>
-  </si>
-  <si>
-    <t>5.09</t>
-  </si>
-  <si>
-    <t>19.3</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>42.1%</t>
-  </si>
-  <si>
-    <t>17.9%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>4.7%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 4.627,20</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>31.9</t>
+  </si>
+  <si>
+    <t>5.07</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>41.4%</t>
+  </si>
+  <si>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.3%</t>
+    <t>6.7%</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>1101.0</t>
-  </si>
-  <si>
-    <t>905.0</t>
-  </si>
-  <si>
-    <t>84.0</t>
-  </si>
-  <si>
-    <t>13.0</t>
-  </si>
-  <si>
-    <t>238.0</t>
-  </si>
-  <si>
-    <t>58.0</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>317.0</t>
-  </si>
-  <si>
-    <t>141.0</t>
-  </si>
-  <si>
-    <t>206.0</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>50.0</t>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>1299.0</t>
+  </si>
+  <si>
+    <t>1058.0</t>
+  </si>
+  <si>
+    <t>108.0</t>
+  </si>
+  <si>
+    <t>14.0</t>
+  </si>
+  <si>
+    <t>281.0</t>
+  </si>
+  <si>
+    <t>69.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>387.0</t>
+  </si>
+  <si>
+    <t>163.0</t>
+  </si>
+  <si>
+    <t>232.0</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>51.0</t>
   </si>
   <si>
     <t>1</t>
@@ -5787,7 +5787,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>51</v>
@@ -5817,35 +5817,93 @@
         <v>58</v>
       </c>
       <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="6"/>
-      <c r="AL30" s="6"/>
-      <c r="AM30" s="6"/>
-      <c r="AN30" s="9"/>
-      <c r="AO30" s="6"/>
+      <c r="M30" s="5">
+        <v>4401.7200000000003</v>
+      </c>
+      <c r="N30" s="6">
+        <v>34</v>
+      </c>
+      <c r="O30" s="6">
+        <v>12</v>
+      </c>
+      <c r="P30" s="7">
+        <v>3.1185714285714288</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>23.073608333333336</v>
+      </c>
+      <c r="R30" s="8">
+        <v>12.755558333333333</v>
+      </c>
+      <c r="S30" s="8">
+        <v>7</v>
+      </c>
+      <c r="T30" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U30" s="9">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="V30" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="W30" s="9">
+        <v>0</v>
+      </c>
+      <c r="X30" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF30" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP30" s="4">
         <v>58</v>
       </c>
@@ -6611,7 +6669,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6641,35 +6699,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>2459.5599999999999</v>
+      </c>
+      <c r="N36" s="6">
+        <v>34</v>
+      </c>
+      <c r="O36" s="6">
+        <v>15</v>
+      </c>
+      <c r="P36" s="7">
+        <v>4.4854156249999999</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>21.751113333333333</v>
+      </c>
+      <c r="R36" s="8">
+        <v>9.0733333333333324</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7022,7 +7138,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7052,35 +7168,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>6664.1499999999996</v>
+      </c>
+      <c r="N39" s="6">
+        <v>77</v>
+      </c>
+      <c r="O39" s="6">
+        <v>46</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.2549554054054055</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>13.696015217391304</v>
+      </c>
+      <c r="R39" s="8">
+        <v>5.756480555555556</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.63043478260869568</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.41304347826086957</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>8</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7435,7 +7609,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7465,35 +7639,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>5580.8599999999997</v>
+      </c>
+      <c r="N42" s="6">
+        <v>51</v>
+      </c>
+      <c r="O42" s="6">
+        <v>36</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.015625</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>18.368519444444445</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.4025242424242421</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8005,7 +8237,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -8033,35 +8265,93 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="M46" s="5">
+        <v>6684.4099999999999</v>
+      </c>
+      <c r="N46" s="6">
+        <v>64</v>
+      </c>
+      <c r="O46" s="6">
+        <v>34</v>
+      </c>
+      <c r="P46" s="7">
+        <v>4.7666666666666666</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>19.169608823529412</v>
+      </c>
+      <c r="R46" s="8">
+        <v>7.624242424242424</v>
+      </c>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.20588235294117646</v>
+      </c>
+      <c r="U46" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -8569,7 +8859,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8599,35 +8889,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>5771.6400000000003</v>
+      </c>
+      <c r="N50" s="6">
+        <v>65</v>
+      </c>
+      <c r="O50" s="6">
+        <v>29</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.8522442307692306</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>14.549999999999999</v>
+      </c>
+      <c r="R50" s="8">
+        <v>3.9791678571428575</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8668,7 +9016,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -8698,35 +9046,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>917.69000000000005</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
+      <c r="O51" s="6">
+        <v>5</v>
+      </c>
+      <c r="P51" s="7">
+        <v>2.1388888888888888</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>14.073339999999998</v>
+      </c>
+      <c r="R51" s="8">
+        <v>5.5499999999999998</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -9079,7 +9485,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>51</v>
@@ -9109,35 +9515,93 @@
         <v>58</v>
       </c>
       <c r="L54" s="4"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8"/>
-      <c r="T54" s="9"/>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
-      <c r="Y54" s="9"/>
-      <c r="Z54" s="9"/>
-      <c r="AA54" s="9"/>
-      <c r="AB54" s="9"/>
-      <c r="AC54" s="9"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="6"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="6"/>
-      <c r="AM54" s="6"/>
-      <c r="AN54" s="9"/>
-      <c r="AO54" s="6"/>
+      <c r="M54" s="5">
+        <v>2605.79</v>
+      </c>
+      <c r="N54" s="6">
+        <v>31</v>
+      </c>
+      <c r="O54" s="6">
+        <v>25</v>
+      </c>
+      <c r="P54" s="7">
+        <v>5.6021516129032252</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>27.495999999999999</v>
+      </c>
+      <c r="R54" s="8">
+        <v>15.719445833333333</v>
+      </c>
+      <c r="S54" s="8">
+        <v>7</v>
+      </c>
+      <c r="T54" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="U54" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V54" s="9">
+        <v>0</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0</v>
+      </c>
+      <c r="X54" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB54" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP54" s="4">
         <v>58</v>
       </c>
@@ -9178,7 +9642,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9208,35 +9672,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>2752</v>
+      </c>
+      <c r="N55" s="6">
+        <v>40</v>
+      </c>
+      <c r="O55" s="6">
+        <v>34</v>
+      </c>
+      <c r="P55" s="7">
+        <v>2.1418707317073169</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>29.57255</v>
+      </c>
+      <c r="R55" s="8">
+        <v>20.72009705882353</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>11</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9621,33 +10143,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>52</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.096153846153846159</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -10155,7 +10723,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -10185,35 +10753,93 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="M62" s="5">
+        <v>3369.1799999999998</v>
+      </c>
+      <c r="N62" s="6">
+        <v>32</v>
+      </c>
+      <c r="O62" s="6">
+        <v>23</v>
+      </c>
+      <c r="P62" s="7">
+        <v>2.7215676470588233</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>12.631160869565218</v>
+      </c>
+      <c r="R62" s="8">
+        <v>3.1181818181818177</v>
+      </c>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -11231,7 +11857,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11261,35 +11887,93 @@
         <v>58</v>
       </c>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="8"/>
-      <c r="T70" s="9"/>
-      <c r="U70" s="9"/>
-      <c r="V70" s="9"/>
-      <c r="W70" s="9"/>
-      <c r="X70" s="9"/>
-      <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
-      <c r="AA70" s="9"/>
-      <c r="AB70" s="9"/>
-      <c r="AC70" s="9"/>
-      <c r="AD70" s="6"/>
-      <c r="AE70" s="6"/>
-      <c r="AF70" s="6"/>
-      <c r="AG70" s="6"/>
-      <c r="AH70" s="6"/>
-      <c r="AI70" s="6"/>
-      <c r="AJ70" s="6"/>
-      <c r="AK70" s="6"/>
-      <c r="AL70" s="6"/>
-      <c r="AM70" s="6"/>
-      <c r="AN70" s="9"/>
-      <c r="AO70" s="6"/>
+      <c r="M70" s="5">
+        <v>4451.1199999999999</v>
+      </c>
+      <c r="N70" s="6">
+        <v>50</v>
+      </c>
+      <c r="O70" s="6">
+        <v>34</v>
+      </c>
+      <c r="P70" s="7">
+        <v>8.0766659999999995</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>25.207844117647056</v>
+      </c>
+      <c r="R70" s="8">
+        <v>9.412255882352941</v>
+      </c>
+      <c r="S70" s="8">
+        <v>7</v>
+      </c>
+      <c r="T70" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="U70" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="V70" s="9">
+        <v>0</v>
+      </c>
+      <c r="W70" s="9">
+        <v>0</v>
+      </c>
+      <c r="X70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP70" s="4">
         <v>58</v>
       </c>
@@ -11330,7 +12014,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11358,35 +12042,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>5941.1300000000001</v>
+      </c>
+      <c r="N71" s="6">
+        <v>70</v>
+      </c>
+      <c r="O71" s="6">
+        <v>28</v>
+      </c>
+      <c r="P71" s="7">
+        <v>3.7176772727272729</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>15.013689285714287</v>
+      </c>
+      <c r="R71" s="8">
+        <v>4.7406680000000003</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0.035714285714000003</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11834,7 +12576,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11864,35 +12606,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>4298.54</v>
+      </c>
+      <c r="N75" s="6">
+        <v>50</v>
+      </c>
+      <c r="O75" s="6">
+        <v>30</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.4850346938775516</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>24.113890000000001</v>
+      </c>
+      <c r="R75" s="8">
+        <v>11.82389</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -11933,7 +12733,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -11961,35 +12761,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>6783.8199999999997</v>
+      </c>
+      <c r="N76" s="6">
+        <v>80</v>
+      </c>
+      <c r="O76" s="6">
+        <v>47</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.08770875</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>15.428014893617021</v>
+      </c>
+      <c r="R76" s="8">
+        <v>4.1769833333333333</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.53191489361702127</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.19148936170212766</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.042553191489361701</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.042553191489361701</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>9</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -15761,7 +16619,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -15791,14 +16649,26 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
+      <c r="M102" s="5">
+        <v>2728.5999999999999</v>
+      </c>
+      <c r="N102" s="6">
+        <v>28</v>
+      </c>
       <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
+      <c r="P102" s="7">
+        <v>7.0097689655172415</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>49.75</v>
+      </c>
+      <c r="R102" s="8">
+        <v>37.454165000000003</v>
+      </c>
       <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
+      <c r="T102" s="9">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="U102" s="9"/>
       <c r="V102" s="9"/>
       <c r="W102" s="9"/>
@@ -15860,7 +16730,7 @@
         <v>19720</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>51</v>
@@ -15890,35 +16760,93 @@
         <v>58</v>
       </c>
       <c r="L103" s="4"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="6"/>
-      <c r="O103" s="6"/>
-      <c r="P103" s="7"/>
-      <c r="Q103" s="8"/>
-      <c r="R103" s="8"/>
-      <c r="S103" s="8"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
-      <c r="V103" s="9"/>
-      <c r="W103" s="9"/>
-      <c r="X103" s="9"/>
-      <c r="Y103" s="9"/>
-      <c r="Z103" s="9"/>
-      <c r="AA103" s="9"/>
-      <c r="AB103" s="9"/>
-      <c r="AC103" s="9"/>
-      <c r="AD103" s="6"/>
-      <c r="AE103" s="6"/>
-      <c r="AF103" s="6"/>
-      <c r="AG103" s="6"/>
-      <c r="AH103" s="6"/>
-      <c r="AI103" s="6"/>
-      <c r="AJ103" s="6"/>
-      <c r="AK103" s="6"/>
-      <c r="AL103" s="6"/>
-      <c r="AM103" s="6"/>
-      <c r="AN103" s="9"/>
-      <c r="AO103" s="6"/>
+      <c r="M103" s="5">
+        <v>4527.6499999999996</v>
+      </c>
+      <c r="N103" s="6">
+        <v>48</v>
+      </c>
+      <c r="O103" s="6">
+        <v>32</v>
+      </c>
+      <c r="P103" s="7">
+        <v>6.6187499999999995</v>
+      </c>
+      <c r="Q103" s="8">
+        <v>14.288170967741936</v>
+      </c>
+      <c r="R103" s="8">
+        <v>1.6781620689655172</v>
+      </c>
+      <c r="S103" s="8">
+        <v>6</v>
+      </c>
+      <c r="T103" s="9">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="U103" s="9">
+        <v>0.21875</v>
+      </c>
+      <c r="V103" s="9">
+        <v>0</v>
+      </c>
+      <c r="W103" s="9">
+        <v>0</v>
+      </c>
+      <c r="X103" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y103" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="9">
+        <v>0.15625</v>
+      </c>
+      <c r="AB103" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE103" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK103" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL103" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM103" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN103" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP103" s="4">
         <v>58</v>
       </c>
@@ -19165,7 +20093,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>51</v>
@@ -19195,35 +20123,93 @@
         <v>58</v>
       </c>
       <c r="L126" s="4"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="6"/>
-      <c r="O126" s="6"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="9"/>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="M126" s="5">
+        <v>2482.1199999999999</v>
+      </c>
+      <c r="N126" s="6">
+        <v>31</v>
+      </c>
+      <c r="O126" s="6">
+        <v>21</v>
+      </c>
+      <c r="P126" s="7">
+        <v>6.3171727272727276</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>23.730157142857145</v>
+      </c>
+      <c r="R126" s="8">
+        <v>12.25087894736842</v>
+      </c>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
+      <c r="T126" s="9">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="U126" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -20677,7 +21663,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -20707,35 +21693,93 @@
         <v>58</v>
       </c>
       <c r="L136" s="4"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8"/>
-      <c r="S136" s="8"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="M136" s="5">
+        <v>3912.3000000000002</v>
+      </c>
+      <c r="N136" s="6">
+        <v>41</v>
+      </c>
+      <c r="O136" s="6">
+        <v>16</v>
+      </c>
+      <c r="P136" s="7">
+        <v>6.2416666666666663</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>25.672918750000001</v>
+      </c>
+      <c r="R136" s="8">
+        <v>11.369793749999999</v>
+      </c>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
+      <c r="T136" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U136" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -21086,7 +22130,7 @@
         <v>19790</v>
       </c>
       <c r="B139" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C139" s="4">
         <v>51</v>
@@ -21116,35 +22160,93 @@
         <v>58</v>
       </c>
       <c r="L139" s="4"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="6"/>
-      <c r="O139" s="6"/>
-      <c r="P139" s="7"/>
-      <c r="Q139" s="8"/>
-      <c r="R139" s="8"/>
-      <c r="S139" s="8"/>
-      <c r="T139" s="9"/>
-      <c r="U139" s="9"/>
-      <c r="V139" s="9"/>
-      <c r="W139" s="9"/>
-      <c r="X139" s="9"/>
-      <c r="Y139" s="9"/>
-      <c r="Z139" s="9"/>
-      <c r="AA139" s="9"/>
-      <c r="AB139" s="9"/>
-      <c r="AC139" s="9"/>
-      <c r="AD139" s="6"/>
-      <c r="AE139" s="6"/>
-      <c r="AF139" s="6"/>
-      <c r="AG139" s="6"/>
-      <c r="AH139" s="6"/>
-      <c r="AI139" s="6"/>
-      <c r="AJ139" s="6"/>
-      <c r="AK139" s="6"/>
-      <c r="AL139" s="6"/>
-      <c r="AM139" s="6"/>
-      <c r="AN139" s="9"/>
-      <c r="AO139" s="6"/>
+      <c r="M139" s="5">
+        <v>4966.1000000000004</v>
+      </c>
+      <c r="N139" s="6">
+        <v>48</v>
+      </c>
+      <c r="O139" s="6">
+        <v>21</v>
+      </c>
+      <c r="P139" s="7">
+        <v>2.5957446808510638</v>
+      </c>
+      <c r="Q139" s="8">
+        <v>12.020633333333333</v>
+      </c>
+      <c r="R139" s="8">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="S139" s="8">
+        <v>7</v>
+      </c>
+      <c r="T139" s="9">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="U139" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V139" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="W139" s="9">
+        <v>0</v>
+      </c>
+      <c r="X139" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y139" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK139" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM139" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN139" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO139" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP139" s="4">
         <v>58</v>
       </c>
@@ -21383,7 +22485,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>51</v>
@@ -21411,35 +22513,93 @@
         <v>58</v>
       </c>
       <c r="L142" s="4"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="6"/>
-      <c r="O142" s="6"/>
-      <c r="P142" s="7"/>
-      <c r="Q142" s="8"/>
-      <c r="R142" s="8"/>
-      <c r="S142" s="8"/>
-      <c r="T142" s="9"/>
-      <c r="U142" s="9"/>
-      <c r="V142" s="9"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="9"/>
-      <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
-      <c r="AA142" s="9"/>
-      <c r="AB142" s="9"/>
-      <c r="AC142" s="9"/>
-      <c r="AD142" s="6"/>
-      <c r="AE142" s="6"/>
-      <c r="AF142" s="6"/>
-      <c r="AG142" s="6"/>
-      <c r="AH142" s="6"/>
-      <c r="AI142" s="6"/>
-      <c r="AJ142" s="6"/>
-      <c r="AK142" s="6"/>
-      <c r="AL142" s="6"/>
-      <c r="AM142" s="6"/>
-      <c r="AN142" s="9"/>
-      <c r="AO142" s="6"/>
+      <c r="M142" s="5">
+        <v>8306.7999999999993</v>
+      </c>
+      <c r="N142" s="6">
+        <v>81</v>
+      </c>
+      <c r="O142" s="6">
+        <v>46</v>
+      </c>
+      <c r="P142" s="7">
+        <v>5.9845385542168676</v>
+      </c>
+      <c r="Q142" s="8">
+        <v>23.317391304347826</v>
+      </c>
+      <c r="R142" s="8">
+        <v>9.3217046511627917</v>
+      </c>
+      <c r="S142" s="8">
+        <v>8.9000000000000004</v>
+      </c>
+      <c r="T142" s="9">
+        <v>0.15217391304347827</v>
+      </c>
+      <c r="U142" s="9">
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="V142" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="W142" s="9">
+        <v>0</v>
+      </c>
+      <c r="X142" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="Y142" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="9">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="AB142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF142" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK142" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP142" s="4">
         <v>58</v>
       </c>
@@ -24277,7 +25437,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24307,35 +25467,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>3103.0799999999999</v>
+      </c>
+      <c r="N162" s="6">
+        <v>36</v>
+      </c>
+      <c r="O162" s="6">
+        <v>16</v>
+      </c>
+      <c r="P162" s="7">
+        <v>3.2130218749999999</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>15.751043749999999</v>
+      </c>
+      <c r="R162" s="8">
+        <v>4.6369071428571429</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -25731,7 +26949,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>51</v>
@@ -25761,35 +26979,93 @@
         <v>58</v>
       </c>
       <c r="L172" s="4"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="7"/>
-      <c r="Q172" s="8"/>
-      <c r="R172" s="8"/>
-      <c r="S172" s="8"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
-      <c r="V172" s="9"/>
-      <c r="W172" s="9"/>
-      <c r="X172" s="9"/>
-      <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-      <c r="AA172" s="9"/>
-      <c r="AB172" s="9"/>
-      <c r="AC172" s="9"/>
-      <c r="AD172" s="6"/>
-      <c r="AE172" s="6"/>
-      <c r="AF172" s="6"/>
-      <c r="AG172" s="6"/>
-      <c r="AH172" s="6"/>
-      <c r="AI172" s="6"/>
-      <c r="AJ172" s="6"/>
-      <c r="AK172" s="6"/>
-      <c r="AL172" s="6"/>
-      <c r="AM172" s="6"/>
-      <c r="AN172" s="9"/>
-      <c r="AO172" s="6"/>
+      <c r="M172" s="5">
+        <v>1722.28</v>
+      </c>
+      <c r="N172" s="6">
+        <v>21</v>
+      </c>
+      <c r="O172" s="6">
+        <v>19</v>
+      </c>
+      <c r="P172" s="7">
+        <v>3.8769857142857145</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>13.273684210526316</v>
+      </c>
+      <c r="R172" s="8">
+        <v>2.7314833333333333</v>
+      </c>
+      <c r="S172" s="8">
+        <v>7</v>
+      </c>
+      <c r="T172" s="9">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="U172" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="V172" s="9">
+        <v>0</v>
+      </c>
+      <c r="W172" s="9">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y172" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="AB172" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AC172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD172" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP172" s="4">
         <v>58</v>
       </c>
@@ -26142,7 +27418,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -26172,35 +27448,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>2687.3000000000002</v>
+      </c>
+      <c r="N175" s="6">
+        <v>41</v>
+      </c>
+      <c r="O175" s="6">
+        <v>20</v>
+      </c>
+      <c r="P175" s="7">
+        <v>4.515657575757575</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>14.994999999999999</v>
+      </c>
+      <c r="R175" s="8">
+        <v>3.1975000000000002</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -27020,7 +28354,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -27050,35 +28384,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>2820.8800000000001</v>
+      </c>
+      <c r="N181" s="6">
+        <v>30</v>
+      </c>
+      <c r="O181" s="6">
+        <v>13</v>
+      </c>
+      <c r="P181" s="7">
+        <v>4.9637931034482756</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>12.817946153846153</v>
+      </c>
+      <c r="R181" s="8">
+        <v>0.90555555555555556</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27846,7 +29238,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27876,35 +29268,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1119.5999999999999</v>
+      </c>
+      <c r="N187" s="6">
+        <v>13</v>
+      </c>
+      <c r="O187" s="6">
+        <v>9</v>
+      </c>
+      <c r="P187" s="7">
+        <v>12.289285714285715</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>27.538888888888888</v>
+      </c>
+      <c r="R187" s="8">
+        <v>10.038888888888888</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -28102,7 +29552,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -28132,35 +29582,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>5123.29</v>
+      </c>
+      <c r="N189" s="6">
+        <v>70</v>
+      </c>
+      <c r="O189" s="6">
+        <v>60</v>
+      </c>
+      <c r="P189" s="7">
+        <v>5.2019042857142859</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>26.688333333333333</v>
+      </c>
+      <c r="R189" s="8">
+        <v>17.332703773584903</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>35</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>25</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>20</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28201,7 +29709,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28231,35 +29739,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3001.1900000000001</v>
+      </c>
+      <c r="N190" s="6">
+        <v>35</v>
+      </c>
+      <c r="O190" s="6">
+        <v>11</v>
+      </c>
+      <c r="P190" s="7">
+        <v>4.0151970588235288</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>17.12879090909091</v>
+      </c>
+      <c r="R190" s="8">
+        <v>5.9033299999999995</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -28926,7 +30492,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -28956,14 +30522,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>4373.6400000000003</v>
+      </c>
+      <c r="N195" s="6">
+        <v>45</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>6.042064285714285</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>26.136111111111109</v>
+      </c>
+      <c r="R195" s="8">
+        <v>13.106944444444444</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
@@ -29653,7 +31231,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -29683,35 +31261,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>1397.2</v>
+      </c>
+      <c r="N200" s="6">
+        <v>17</v>
+      </c>
+      <c r="O200" s="6">
+        <v>10</v>
+      </c>
+      <c r="P200" s="7">
+        <v>9.1294117647058819</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>19.551669999999998</v>
+      </c>
+      <c r="R200" s="8">
+        <v>3.0574111111111111</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
